--- a/mini-project-2-template-26-main/Mini Project 2 - Instructor Database.xlsx
+++ b/mini-project-2-template-26-main/Mini Project 2 - Instructor Database.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -99,7 +99,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -122,7 +122,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +572,7 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>45689</v>
       </c>
       <c r="C3" t="n">
@@ -705,6 +706,19 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10/2</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -719,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +826,14 @@
       </c>
       <c r="B11" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1040,17 @@
         <v>9</v>
       </c>
       <c r="C17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
         <v>3</v>
       </c>
     </row>

--- a/mini-project-2-template-26-main/Mini Project 2 - Instructor Database.xlsx
+++ b/mini-project-2-template-26-main/Mini Project 2 - Instructor Database.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Challenges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Challenge-Users" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Timerecord" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -99,7 +99,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -122,8 +122,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,7 +571,7 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="8" t="n">
         <v>45689</v>
       </c>
       <c r="C3" t="n">
@@ -706,19 +705,6 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10/2</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -733,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,14 +812,6 @@
       </c>
       <c r="B11" t="n">
         <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -847,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,17 +1018,6 @@
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" t="n">
         <v>3</v>
       </c>
     </row>
